--- a/R_Codes/DataSummary/All_Prokaryotes/Sample_name/All_Prokaryotes_Summary_Phylum_by_Sample_name.xlsx
+++ b/R_Codes/DataSummary/All_Prokaryotes/Sample_name/All_Prokaryotes_Summary_Phylum_by_Sample_name.xlsx
@@ -613,10 +613,10 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>23.7666707186631</v>
+        <v>23.7646171113957</v>
       </c>
       <c r="D2" t="n">
-        <v>0.44293662988076</v>
+        <v>0.444192766632351</v>
       </c>
     </row>
     <row r="3">
@@ -627,10 +627,10 @@
         <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>13.5338685482105</v>
+        <v>13.5389810557136</v>
       </c>
       <c r="D3" t="n">
-        <v>0.156874534303187</v>
+        <v>0.156940608357176</v>
       </c>
     </row>
     <row r="4">
@@ -641,10 +641,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>11.5594830877428</v>
+        <v>11.5559776919132</v>
       </c>
       <c r="D4" t="n">
-        <v>0.29013213834009</v>
+        <v>0.289954475563205</v>
       </c>
     </row>
     <row r="5">
@@ -655,10 +655,10 @@
         <v>8</v>
       </c>
       <c r="C5" t="n">
-        <v>7.01538098706899</v>
+        <v>7.01467567205716</v>
       </c>
       <c r="D5" t="n">
-        <v>0.199360754590101</v>
+        <v>0.199253355768674</v>
       </c>
     </row>
     <row r="6">
@@ -669,10 +669,10 @@
         <v>9</v>
       </c>
       <c r="C6" t="n">
-        <v>4.74548686925507</v>
+        <v>4.74931089124792</v>
       </c>
       <c r="D6" t="n">
-        <v>0.686338219370113</v>
+        <v>0.687124957308885</v>
       </c>
     </row>
     <row r="7">
@@ -683,10 +683,10 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>4.44162381048769</v>
+        <v>4.44655644955414</v>
       </c>
       <c r="D7" t="n">
-        <v>0.510079436916076</v>
+        <v>0.510861065646137</v>
       </c>
     </row>
     <row r="8">
@@ -697,10 +697,10 @@
         <v>11</v>
       </c>
       <c r="C8" t="n">
-        <v>4.41212844425493</v>
+        <v>4.4124426862629</v>
       </c>
       <c r="D8" t="n">
-        <v>0.101544966517221</v>
+        <v>0.101516069912201</v>
       </c>
     </row>
     <row r="9">
@@ -711,10 +711,10 @@
         <v>12</v>
       </c>
       <c r="C9" t="n">
-        <v>3.5102933201201</v>
+        <v>3.51042284201482</v>
       </c>
       <c r="D9" t="n">
-        <v>0.278103271520113</v>
+        <v>0.278058789154062</v>
       </c>
     </row>
     <row r="10">
@@ -725,10 +725,10 @@
         <v>13</v>
       </c>
       <c r="C10" t="n">
-        <v>3.29553393669252</v>
+        <v>3.28454697103204</v>
       </c>
       <c r="D10" t="n">
-        <v>0.674755852744477</v>
+        <v>0.716836934972719</v>
       </c>
     </row>
     <row r="11">
@@ -739,10 +739,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>2.37263887034865</v>
+        <v>2.37379349757844</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0355114868860015</v>
+        <v>0.035545954636435</v>
       </c>
     </row>
     <row r="12">
@@ -753,10 +753,10 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>2.08902184937749</v>
+        <v>2.0891099450425</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0706745150316027</v>
+        <v>0.0706662999116921</v>
       </c>
     </row>
     <row r="13">
@@ -767,10 +767,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>1.65181412581786</v>
+        <v>1.65213774608583</v>
       </c>
       <c r="D13" t="n">
-        <v>0.249286546400501</v>
+        <v>0.249357480884307</v>
       </c>
     </row>
     <row r="14">
@@ -781,10 +781,10 @@
         <v>17</v>
       </c>
       <c r="C14" t="n">
-        <v>1.64819405359042</v>
+        <v>1.64855580829204</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0857502230484642</v>
+        <v>0.0857648351672002</v>
       </c>
     </row>
     <row r="15">
@@ -795,10 +795,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="n">
-        <v>1.53539813331544</v>
+        <v>1.53475915954153</v>
       </c>
       <c r="D15" t="n">
-        <v>0.11437526543458</v>
+        <v>0.114297343440791</v>
       </c>
     </row>
     <row r="16">
@@ -809,10 +809,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.49213500624218</v>
+        <v>1.4919442619445</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0305929966125898</v>
+        <v>0.0305772187518557</v>
       </c>
     </row>
     <row r="17">
@@ -823,10 +823,10 @@
         <v>20</v>
       </c>
       <c r="C17" t="n">
-        <v>1.39903086442211</v>
+        <v>1.39901428902687</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0919059866165108</v>
+        <v>0.0919138887798784</v>
       </c>
     </row>
     <row r="18">
@@ -837,10 +837,10 @@
         <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>1.31561220963714</v>
+        <v>1.31536584951405</v>
       </c>
       <c r="D18" t="n">
-        <v>0.224020070752134</v>
+        <v>0.223995295658811</v>
       </c>
     </row>
     <row r="19">
@@ -851,10 +851,10 @@
         <v>22</v>
       </c>
       <c r="C19" t="n">
-        <v>1.1219355744175</v>
+        <v>1.12227527386278</v>
       </c>
       <c r="D19" t="n">
-        <v>0.130011254159124</v>
+        <v>0.130044278882783</v>
       </c>
     </row>
     <row r="20">
@@ -865,10 +865,10 @@
         <v>23</v>
       </c>
       <c r="C20" t="n">
-        <v>0.942019245174214</v>
+        <v>0.94151232214195</v>
       </c>
       <c r="D20" t="n">
-        <v>0.370427466384496</v>
+        <v>0.370227991956522</v>
       </c>
     </row>
     <row r="21">
@@ -879,10 +879,10 @@
         <v>24</v>
       </c>
       <c r="C21" t="n">
-        <v>0.729901630188444</v>
+        <v>0.730483140491789</v>
       </c>
       <c r="D21" t="n">
-        <v>0.114986922000628</v>
+        <v>0.115145981293474</v>
       </c>
     </row>
     <row r="22">
@@ -893,10 +893,10 @@
         <v>25</v>
       </c>
       <c r="C22" t="n">
-        <v>0.722732699304359</v>
+        <v>0.722971476354408</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0574180187638795</v>
+        <v>0.0574018097724355</v>
       </c>
     </row>
     <row r="23">
@@ -907,10 +907,10 @@
         <v>26</v>
       </c>
       <c r="C23" t="n">
-        <v>0.684432795181612</v>
+        <v>0.684459236763228</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0666667909892136</v>
+        <v>0.0666702180830657</v>
       </c>
     </row>
     <row r="24">
@@ -921,10 +921,10 @@
         <v>27</v>
       </c>
       <c r="C24" t="n">
-        <v>0.655040031421386</v>
+        <v>0.65488059499132</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0499614906311154</v>
+        <v>0.0499389194021385</v>
       </c>
     </row>
     <row r="25">
@@ -935,10 +935,10 @@
         <v>28</v>
       </c>
       <c r="C25" t="n">
-        <v>0.538901045976734</v>
+        <v>0.538824251893525</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0171736367669633</v>
+        <v>0.0171725141860427</v>
       </c>
     </row>
     <row r="26">
@@ -949,10 +949,10 @@
         <v>29</v>
       </c>
       <c r="C26" t="n">
-        <v>0.501447759387826</v>
+        <v>0.501562110209772</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0321522457219686</v>
+        <v>0.0321531672948795</v>
       </c>
     </row>
     <row r="27">
@@ -963,10 +963,10 @@
         <v>30</v>
       </c>
       <c r="C27" t="n">
-        <v>0.433738318060491</v>
+        <v>0.433650563444163</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0140375569528617</v>
+        <v>0.0140318235642723</v>
       </c>
     </row>
     <row r="28">
@@ -977,10 +977,10 @@
         <v>31</v>
       </c>
       <c r="C28" t="n">
-        <v>0.408033161711585</v>
+        <v>0.407980180797016</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0310715690382773</v>
+        <v>0.0310616201315237</v>
       </c>
     </row>
     <row r="29">
@@ -991,10 +991,10 @@
         <v>32</v>
       </c>
       <c r="C29" t="n">
-        <v>0.357219140056316</v>
+        <v>0.357279560126297</v>
       </c>
       <c r="D29" t="n">
-        <v>0.252127639540736</v>
+        <v>0.252170677786732</v>
       </c>
     </row>
     <row r="30">
@@ -1005,10 +1005,10 @@
         <v>33</v>
       </c>
       <c r="C30" t="n">
-        <v>0.357097557107273</v>
+        <v>0.357069985177181</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0188894802691344</v>
+        <v>0.0188826601470137</v>
       </c>
     </row>
     <row r="31">
@@ -1019,10 +1019,10 @@
         <v>34</v>
       </c>
       <c r="C31" t="n">
-        <v>0.237883538286618</v>
+        <v>0.237866930091988</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0433817185157511</v>
+        <v>0.0433784063794467</v>
       </c>
     </row>
     <row r="32">
@@ -1033,10 +1033,10 @@
         <v>35</v>
       </c>
       <c r="C32" t="n">
-        <v>0.237354733382793</v>
+        <v>0.237535707569507</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0633840758585622</v>
+        <v>0.0634142931010395</v>
       </c>
     </row>
     <row r="33">
@@ -1047,10 +1047,10 @@
         <v>36</v>
       </c>
       <c r="C33" t="n">
-        <v>0.215403885861381</v>
+        <v>0.21556989052782</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0140755165261721</v>
+        <v>0.0140897760127736</v>
       </c>
     </row>
     <row r="34">
@@ -1061,10 +1061,10 @@
         <v>37</v>
       </c>
       <c r="C34" t="n">
-        <v>0.213040399651461</v>
+        <v>0.213086799871348</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00887995723498081</v>
+        <v>0.00888454748100951</v>
       </c>
     </row>
     <row r="35">
@@ -1075,10 +1075,10 @@
         <v>38</v>
       </c>
       <c r="C35" t="n">
-        <v>0.196346163221418</v>
+        <v>0.196525967818807</v>
       </c>
       <c r="D35" t="n">
-        <v>0.042057155666971</v>
+        <v>0.0421406587788283</v>
       </c>
     </row>
     <row r="36">
@@ -1089,10 +1089,10 @@
         <v>39</v>
       </c>
       <c r="C36" t="n">
-        <v>0.1762094470845</v>
+        <v>0.176457205964325</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0987560773911232</v>
+        <v>0.0988979998929312</v>
       </c>
     </row>
     <row r="37">
@@ -1103,10 +1103,10 @@
         <v>40</v>
       </c>
       <c r="C37" t="n">
-        <v>0.173365122136209</v>
+        <v>0.173777381480502</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0767428536724862</v>
+        <v>0.0769494542869134</v>
       </c>
     </row>
     <row r="38">
@@ -1117,10 +1117,10 @@
         <v>41</v>
       </c>
       <c r="C38" t="n">
-        <v>0.158452941556705</v>
+        <v>0.158406264655942</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0320443011426758</v>
+        <v>0.0320277246410673</v>
       </c>
     </row>
     <row r="39">
@@ -1131,7 +1131,7 @@
         <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>0.135992760059572</v>
+        <v>0.135993949067377</v>
       </c>
       <c r="D39"/>
     </row>
@@ -1143,10 +1143,10 @@
         <v>43</v>
       </c>
       <c r="C40" t="n">
-        <v>0.11958131801605</v>
+        <v>0.119661904634684</v>
       </c>
       <c r="D40" t="n">
-        <v>0.00866643145246178</v>
+        <v>0.00867449478346747</v>
       </c>
     </row>
     <row r="41">
@@ -1157,10 +1157,10 @@
         <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>0.092568372503675</v>
+        <v>0.092680306221937</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0302793212763506</v>
+        <v>0.0303196519633</v>
       </c>
     </row>
     <row r="42">
@@ -1171,10 +1171,10 @@
         <v>45</v>
       </c>
       <c r="C42" t="n">
-        <v>0.0921394725886354</v>
+        <v>0.0921400478814066</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0361739085241452</v>
+        <v>0.0361939575663574</v>
       </c>
     </row>
     <row r="43">
@@ -1185,10 +1185,10 @@
         <v>46</v>
       </c>
       <c r="C43" t="n">
-        <v>0.0720310555084331</v>
+        <v>0.072038104960379</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00501667168349076</v>
+        <v>0.0050163514780864</v>
       </c>
     </row>
     <row r="44">
@@ -1199,10 +1199,10 @@
         <v>47</v>
       </c>
       <c r="C44" t="n">
-        <v>0.0681086689212079</v>
+        <v>0.0680993114124898</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00915704037719756</v>
+        <v>0.00915575781347932</v>
       </c>
     </row>
     <row r="45">
@@ -1213,10 +1213,10 @@
         <v>48</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0649945465535196</v>
+        <v>0.065033567108896</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00434718561093383</v>
+        <v>0.00435059276688745</v>
       </c>
     </row>
     <row r="46">
@@ -1227,10 +1227,10 @@
         <v>49</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0607931420570137</v>
+        <v>0.0608148665136722</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0083334688702682</v>
+        <v>0.00833335922378025</v>
       </c>
     </row>
     <row r="47">
@@ -1241,10 +1241,10 @@
         <v>50</v>
       </c>
       <c r="C47" t="n">
-        <v>0.0596098785521259</v>
+        <v>0.059582510919524</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0124203080559801</v>
+        <v>0.0124120724949685</v>
       </c>
     </row>
     <row r="48">
@@ -1255,10 +1255,10 @@
         <v>51</v>
       </c>
       <c r="C48" t="n">
-        <v>0.0443305459127035</v>
+        <v>0.0443330416683277</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0154167540084506</v>
+        <v>0.0154125372708621</v>
       </c>
     </row>
     <row r="49">
@@ -1269,10 +1269,10 @@
         <v>52</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0415121658534988</v>
+        <v>0.0415713182743147</v>
       </c>
       <c r="D49" t="n">
-        <v>0.00669141911191948</v>
+        <v>0.00670402056267716</v>
       </c>
     </row>
     <row r="50">
@@ -1283,10 +1283,10 @@
         <v>53</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0374889914646262</v>
+        <v>0.0375223949531177</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00476323010424525</v>
+        <v>0.00476729851308149</v>
       </c>
     </row>
     <row r="51">
@@ -1297,10 +1297,10 @@
         <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0350908793724853</v>
+        <v>0.0351076759182588</v>
       </c>
       <c r="D51" t="n">
-        <v>0.000794947062707524</v>
+        <v>0.000795127397304217</v>
       </c>
     </row>
     <row r="52">
@@ -1311,10 +1311,10 @@
         <v>55</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0291765236544047</v>
+        <v>0.029189291118077</v>
       </c>
       <c r="D52" t="n">
-        <v>0.0139655288351434</v>
+        <v>0.013951834600167</v>
       </c>
     </row>
     <row r="53">
@@ -1325,10 +1325,10 @@
         <v>56</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0280719776296357</v>
+        <v>0.0280773577994149</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00443122716905393</v>
+        <v>0.00443189033087297</v>
       </c>
     </row>
     <row r="54">
@@ -1339,10 +1339,10 @@
         <v>57</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0226663183002104</v>
+        <v>0.0226923206597295</v>
       </c>
       <c r="D54" t="n">
-        <v>0.000510630741798756</v>
+        <v>0.000488589558150084</v>
       </c>
     </row>
     <row r="55">
@@ -1353,10 +1353,10 @@
         <v>58</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0212579375157307</v>
+        <v>0.0212618098926915</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00483788808695239</v>
+        <v>0.00483651825215603</v>
       </c>
     </row>
     <row r="56">
@@ -1367,10 +1367,10 @@
         <v>59</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0204730678370141</v>
+        <v>0.0204884508837802</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00375852070875376</v>
+        <v>0.0037621171971516</v>
       </c>
     </row>
     <row r="57">
@@ -1381,7 +1381,7 @@
         <v>60</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0180970260664018</v>
+        <v>0.0181067658797221</v>
       </c>
       <c r="D57"/>
     </row>
@@ -1393,10 +1393,10 @@
         <v>61</v>
       </c>
       <c r="C58" t="n">
-        <v>0.01374887845431</v>
+        <v>0.0137473030642314</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00245762675404466</v>
+        <v>0.00245600218885046</v>
       </c>
     </row>
     <row r="59">
@@ -1407,10 +1407,10 @@
         <v>62</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0130467479587462</v>
+        <v>0.0130673117536518</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00321573199456767</v>
+        <v>0.00321928941579555</v>
       </c>
     </row>
     <row r="60">
@@ -1421,10 +1421,10 @@
         <v>63</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0125099977391701</v>
+        <v>0.012518182256482</v>
       </c>
       <c r="D60" t="n">
-        <v>0.0022069061650978</v>
+        <v>0.00220871676391359</v>
       </c>
     </row>
     <row r="61">
@@ -1435,7 +1435,7 @@
         <v>64</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0117311115698457</v>
+        <v>0.0117546746425129</v>
       </c>
       <c r="D61"/>
     </row>
@@ -1447,10 +1447,10 @@
         <v>65</v>
       </c>
       <c r="C62" t="n">
-        <v>0.011254883076417</v>
+        <v>0.0112678883013945</v>
       </c>
       <c r="D62" t="n">
-        <v>0.000325299942819365</v>
+        <v>0.000328441143608196</v>
       </c>
     </row>
     <row r="63">
@@ -1461,10 +1461,10 @@
         <v>66</v>
       </c>
       <c r="C63" t="n">
-        <v>0.00526048565892599</v>
+        <v>0.00525922355353452</v>
       </c>
       <c r="D63" t="n">
-        <v>0.000968486027812199</v>
+        <v>0.00096797051640928</v>
       </c>
     </row>
     <row r="64">
@@ -1475,10 +1475,10 @@
         <v>67</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00437355300442919</v>
+        <v>0.0043747545330128</v>
       </c>
       <c r="D64" t="n">
-        <v>0.00262813222459885</v>
+        <v>0.00262929663840066</v>
       </c>
     </row>
     <row r="65">
@@ -1489,7 +1489,7 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00413274127397247</v>
+        <v>0.00413503725608872</v>
       </c>
       <c r="D65"/>
     </row>
@@ -1501,10 +1501,10 @@
         <v>69</v>
       </c>
       <c r="C66" t="n">
-        <v>0.00349515420759013</v>
+        <v>0.00349391239421104</v>
       </c>
       <c r="D66" t="n">
-        <v>0.000966050661745871</v>
+        <v>0.000966192955856591</v>
       </c>
     </row>
     <row r="67">
@@ -1515,10 +1515,10 @@
         <v>70</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00285722382509511</v>
+        <v>0.00286205078429382</v>
       </c>
       <c r="D67" t="n">
-        <v>0.000490743586877791</v>
+        <v>0.000491116369881946</v>
       </c>
     </row>
     <row r="68">
@@ -1529,10 +1529,10 @@
         <v>71</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00269738565206895</v>
+        <v>0.00269555730858107</v>
       </c>
       <c r="D68" t="n">
-        <v>0.000978535520958555</v>
+        <v>0.000977872249451185</v>
       </c>
     </row>
     <row r="69">
@@ -1543,10 +1543,10 @@
         <v>72</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00152579489501191</v>
+        <v>0.00152711325176859</v>
       </c>
       <c r="D69" t="n">
-        <v>0.000382244772894996</v>
+        <v>0.000383649199086497</v>
       </c>
     </row>
     <row r="70">
@@ -1557,10 +1557,10 @@
         <v>73</v>
       </c>
       <c r="C70" t="n">
-        <v>0.00138670282422265</v>
+        <v>0.0013893407583248</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0000293394191498065</v>
+        <v>0.0000309483951927951</v>
       </c>
     </row>
     <row r="71">
@@ -1571,7 +1571,7 @@
         <v>74</v>
       </c>
       <c r="C71" t="n">
-        <v>0.00108149480006132</v>
+        <v>0.00108193802659964</v>
       </c>
       <c r="D71"/>
     </row>
@@ -1583,7 +1583,7 @@
         <v>75</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00100160023612772</v>
+        <v>0.00100121540237271</v>
       </c>
       <c r="D72"/>
     </row>
@@ -1595,7 +1595,7 @@
         <v>76</v>
       </c>
       <c r="C73" t="n">
-        <v>0.000755933034934702</v>
+        <v>0.000756106814783813</v>
       </c>
       <c r="D73"/>
     </row>
@@ -1607,7 +1607,7 @@
         <v>77</v>
       </c>
       <c r="C74" t="n">
-        <v>0.000285639005739292</v>
+        <v>0.000286621679708027</v>
       </c>
       <c r="D74"/>
     </row>
@@ -1644,10 +1644,10 @@
         <v>9</v>
       </c>
       <c r="C2" t="n">
-        <v>18.2027915718889</v>
+        <v>18.6701967120886</v>
       </c>
       <c r="D2" t="n">
-        <v>5.77663965540794</v>
+        <v>5.92472741205995</v>
       </c>
     </row>
     <row r="3">
@@ -1658,10 +1658,10 @@
         <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>15.7941728643622</v>
+        <v>16.1686472181674</v>
       </c>
       <c r="D3" t="n">
-        <v>4.03253025607206</v>
+        <v>4.12818212323637</v>
       </c>
     </row>
     <row r="4">
@@ -1672,10 +1672,10 @@
         <v>5</v>
       </c>
       <c r="C4" t="n">
-        <v>13.9140197600743</v>
+        <v>14.1125665044855</v>
       </c>
       <c r="D4" t="n">
-        <v>0.295886676818641</v>
+        <v>0.301124391904363</v>
       </c>
     </row>
     <row r="5">
@@ -1686,10 +1686,10 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>11.9843198691813</v>
+        <v>11.5675003162001</v>
       </c>
       <c r="D5" t="n">
-        <v>0.943501140912699</v>
+        <v>0.904166644289238</v>
       </c>
     </row>
     <row r="6">
@@ -1700,10 +1700,10 @@
         <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>10.6823484590553</v>
+        <v>10.8796597564902</v>
       </c>
       <c r="D6" t="n">
-        <v>1.00582915340246</v>
+        <v>1.02396205701846</v>
       </c>
     </row>
     <row r="7">
@@ -1714,10 +1714,10 @@
         <v>34</v>
       </c>
       <c r="C7" t="n">
-        <v>9.80284162557101</v>
+        <v>9.98626556533853</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0984346521773611</v>
+        <v>0.100254045538964</v>
       </c>
     </row>
     <row r="8">
@@ -1728,10 +1728,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>2.61178409276851</v>
+        <v>2.62809772055264</v>
       </c>
       <c r="D8" t="n">
-        <v>0.250411123559905</v>
+        <v>0.253272037159169</v>
       </c>
     </row>
     <row r="9">
@@ -1739,13 +1739,13 @@
         <v>78</v>
       </c>
       <c r="B9" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C9" t="n">
-        <v>2.60892333817003</v>
+        <v>2.04509349067059</v>
       </c>
       <c r="D9" t="n">
-        <v>0.26020810847188</v>
+        <v>0.0851895719362891</v>
       </c>
     </row>
     <row r="10">
@@ -1753,13 +1753,13 @@
         <v>78</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>2.03093080902504</v>
+        <v>1.88664973784313</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0839332849812322</v>
+        <v>0.0521588768377038</v>
       </c>
     </row>
     <row r="11">
@@ -1767,13 +1767,13 @@
         <v>78</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>1.85356589603393</v>
+        <v>1.74197463929611</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0511875405587528</v>
+        <v>0.0965728005054837</v>
       </c>
     </row>
     <row r="12">
@@ -1781,13 +1781,13 @@
         <v>78</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
-        <v>1.71110685315273</v>
+        <v>1.61959510115843</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0948526470528022</v>
+        <v>0.0272854376301156</v>
       </c>
     </row>
     <row r="13">
@@ -1795,13 +1795,13 @@
         <v>78</v>
       </c>
       <c r="B13" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>1.63394889275421</v>
+        <v>1.4831227708338</v>
       </c>
       <c r="D13" t="n">
-        <v>0.028370272928757</v>
+        <v>0.156847493133174</v>
       </c>
     </row>
     <row r="14">
@@ -1812,10 +1812,10 @@
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>0.898380195139984</v>
+        <v>0.914430020609492</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0348556471656912</v>
+        <v>0.0355075371065342</v>
       </c>
     </row>
     <row r="15">
@@ -1826,10 +1826,10 @@
         <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>0.72286228644442</v>
+        <v>0.733483989727488</v>
       </c>
       <c r="D15" t="n">
-        <v>0.119709519043444</v>
+        <v>0.122109322214215</v>
       </c>
     </row>
     <row r="16">
@@ -1840,10 +1840,10 @@
         <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>0.70664940377435</v>
+        <v>0.717771377787698</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0220874560505524</v>
+        <v>0.0224540796301357</v>
       </c>
     </row>
     <row r="17">
@@ -1854,10 +1854,10 @@
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>0.618075570650204</v>
+        <v>0.608751531792866</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0255714907708922</v>
+        <v>0.0245354855909901</v>
       </c>
     </row>
     <row r="18">
@@ -1868,10 +1868,10 @@
         <v>79</v>
       </c>
       <c r="C18" t="n">
-        <v>0.59022171376807</v>
+        <v>0.601254113499933</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0202054733286437</v>
+        <v>0.0205709171270145</v>
       </c>
     </row>
     <row r="19">
@@ -1882,10 +1882,10 @@
         <v>28</v>
       </c>
       <c r="C19" t="n">
-        <v>0.526855706384887</v>
+        <v>0.536293704410427</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0180429191389399</v>
+        <v>0.0183211795699311</v>
       </c>
     </row>
     <row r="20">
@@ -1896,10 +1896,10 @@
         <v>33</v>
       </c>
       <c r="C20" t="n">
-        <v>0.483170471322615</v>
+        <v>0.475132534526925</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0532903958354552</v>
+        <v>0.0516817264590292</v>
       </c>
     </row>
     <row r="21">
@@ -1910,10 +1910,10 @@
         <v>12</v>
       </c>
       <c r="C21" t="n">
-        <v>0.404758763610594</v>
+        <v>0.40389086627416</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0497524019338565</v>
+        <v>0.0489488239163188</v>
       </c>
     </row>
     <row r="22">
@@ -1924,10 +1924,10 @@
         <v>22</v>
       </c>
       <c r="C22" t="n">
-        <v>0.40282714785413</v>
+        <v>0.393394861710404</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0946477811499876</v>
+        <v>0.0911584562012848</v>
       </c>
     </row>
     <row r="23">
@@ -1938,10 +1938,10 @@
         <v>19</v>
       </c>
       <c r="C23" t="n">
-        <v>0.290559012615653</v>
+        <v>0.296051062841857</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0214373312672283</v>
+        <v>0.0218399348668751</v>
       </c>
     </row>
     <row r="24">
@@ -1952,10 +1952,10 @@
         <v>30</v>
       </c>
       <c r="C24" t="n">
-        <v>0.222676405564927</v>
+        <v>0.219674132325298</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0132383935548477</v>
+        <v>0.0127563655089097</v>
       </c>
     </row>
     <row r="25">
@@ -1963,13 +1963,13 @@
         <v>78</v>
       </c>
       <c r="B25" t="s">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="C25" t="n">
-        <v>0.187375722668919</v>
+        <v>0.185239512055601</v>
       </c>
       <c r="D25" t="n">
-        <v>0.025162953520189</v>
+        <v>0.0183270734647395</v>
       </c>
     </row>
     <row r="26">
@@ -1977,13 +1977,13 @@
         <v>78</v>
       </c>
       <c r="B26" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="C26" t="n">
-        <v>0.18165726583345</v>
+        <v>0.185013203657803</v>
       </c>
       <c r="D26" t="n">
-        <v>0.017988222251576</v>
+        <v>0.0242359873692432</v>
       </c>
     </row>
     <row r="27">
@@ -1994,10 +1994,10 @@
         <v>29</v>
       </c>
       <c r="C27" t="n">
-        <v>0.143469822218936</v>
+        <v>0.146248778556958</v>
       </c>
       <c r="D27" t="n">
-        <v>0.00500190534289163</v>
+        <v>0.00509910821812543</v>
       </c>
     </row>
     <row r="28">
@@ -2008,10 +2008,10 @@
         <v>37</v>
       </c>
       <c r="C28" t="n">
-        <v>0.112721390572844</v>
+        <v>0.115166082212113</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0136992406951073</v>
+        <v>0.0140169099821498</v>
       </c>
     </row>
     <row r="29">
@@ -2022,10 +2022,10 @@
         <v>54</v>
       </c>
       <c r="C29" t="n">
-        <v>0.109632604220882</v>
+        <v>0.111072277609854</v>
       </c>
       <c r="D29" t="n">
-        <v>0.00375386967910732</v>
+        <v>0.00377827799911721</v>
       </c>
     </row>
     <row r="30">
@@ -2033,13 +2033,13 @@
         <v>78</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0762022049641709</v>
+        <v>0.0743941226966877</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0175851118125976</v>
+        <v>0.02825215523625</v>
       </c>
     </row>
     <row r="31">
@@ -2047,13 +2047,13 @@
         <v>78</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0729773646854068</v>
+        <v>0.0736319471593016</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0277141031745769</v>
+        <v>0.0166506737171187</v>
       </c>
     </row>
     <row r="32">
@@ -2061,13 +2061,13 @@
         <v>78</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>32</v>
       </c>
       <c r="C32" t="n">
-        <v>0.0595077003468171</v>
+        <v>0.059654007312589</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0131829848966438</v>
+        <v>0.0256086462176168</v>
       </c>
     </row>
     <row r="33">
@@ -2075,13 +2075,13 @@
         <v>78</v>
       </c>
       <c r="B33" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C33" t="n">
-        <v>0.0584668043755701</v>
+        <v>0.0582030490783911</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0252007847191451</v>
+        <v>0.0125557585312763</v>
       </c>
     </row>
     <row r="34">
@@ -2092,10 +2092,10 @@
         <v>41</v>
       </c>
       <c r="C34" t="n">
-        <v>0.0535564907720787</v>
+        <v>0.0545293894957624</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0215733440917537</v>
+        <v>0.021957881944754</v>
       </c>
     </row>
     <row r="35">
@@ -2106,10 +2106,10 @@
         <v>31</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0514403495881188</v>
+        <v>0.0526450738739072</v>
       </c>
       <c r="D35" t="n">
-        <v>0.00551911166751127</v>
+        <v>0.00566135012596707</v>
       </c>
     </row>
     <row r="36">
@@ -2120,10 +2120,10 @@
         <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>0.0490028150867934</v>
+        <v>0.0464996246001762</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0334037351412075</v>
+        <v>0.0316116624841636</v>
       </c>
     </row>
     <row r="37">
@@ -2134,10 +2134,10 @@
         <v>46</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0330345283186315</v>
+        <v>0.0327733410171936</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00444657428805936</v>
+        <v>0.00424541341835407</v>
       </c>
     </row>
     <row r="38">
@@ -2148,10 +2148,10 @@
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>0.0318993347259668</v>
+        <v>0.032529098590068</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00325541922710889</v>
+        <v>0.00331751523147826</v>
       </c>
     </row>
     <row r="39">
@@ -2162,10 +2162,10 @@
         <v>27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.0266525287902002</v>
+        <v>0.027170178685697</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00808206999742258</v>
+        <v>0.00823950807632378</v>
       </c>
     </row>
     <row r="40">
@@ -2176,7 +2176,7 @@
         <v>23</v>
       </c>
       <c r="C40" t="n">
-        <v>0.0108635580858995</v>
+        <v>0.0111169858610075</v>
       </c>
       <c r="D40"/>
     </row>
@@ -2188,10 +2188,10 @@
         <v>45</v>
       </c>
       <c r="C41" t="n">
-        <v>0.00938316275613295</v>
+        <v>0.00955618687443777</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0010873169163838</v>
+        <v>0.00110842532950841</v>
       </c>
     </row>
     <row r="42">
@@ -2202,10 +2202,10 @@
         <v>61</v>
       </c>
       <c r="C42" t="n">
-        <v>0.00613280473518975</v>
+        <v>0.00624833178839606</v>
       </c>
       <c r="D42" t="n">
-        <v>0.00231143701672872</v>
+        <v>0.00235486090175442</v>
       </c>
     </row>
     <row r="43">
@@ -2216,10 +2216,10 @@
         <v>56</v>
       </c>
       <c r="C43" t="n">
-        <v>0.00604599557399684</v>
+        <v>0.00618964236678558</v>
       </c>
       <c r="D43" t="n">
-        <v>0.00135426109012268</v>
+        <v>0.00139912815458571</v>
       </c>
     </row>
     <row r="44">
@@ -2230,7 +2230,7 @@
         <v>60</v>
       </c>
       <c r="C44" t="n">
-        <v>0.00509463554022024</v>
+        <v>0.00519689236919798</v>
       </c>
       <c r="D44"/>
     </row>
@@ -2242,7 +2242,7 @@
         <v>59</v>
       </c>
       <c r="C45" t="n">
-        <v>0.00298187230299212</v>
+        <v>0.00303855471955522</v>
       </c>
       <c r="D45"/>
     </row>
@@ -2254,10 +2254,10 @@
         <v>52</v>
       </c>
       <c r="C46" t="n">
-        <v>0.00277032330164156</v>
+        <v>0.00282297360488863</v>
       </c>
       <c r="D46" t="n">
-        <v>0.000303960274740397</v>
+        <v>0.000309940362173772</v>
       </c>
     </row>
     <row r="47">
@@ -2268,7 +2268,7 @@
         <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>0.00245881963555129</v>
+        <v>0.00250653946155477</v>
       </c>
       <c r="D47"/>
     </row>
@@ -2280,10 +2280,10 @@
         <v>36</v>
       </c>
       <c r="C48" t="n">
-        <v>0.001882126801935</v>
+        <v>0.0019181127764312</v>
       </c>
       <c r="D48" t="n">
-        <v>0.000339048168231471</v>
+        <v>0.000345883039138015</v>
       </c>
     </row>
     <row r="49">
@@ -2294,7 +2294,7 @@
         <v>62</v>
       </c>
       <c r="C49" t="n">
-        <v>0.00186869641131444</v>
+        <v>0.00190498324456774</v>
       </c>
       <c r="D49"/>
     </row>
@@ -2306,10 +2306,10 @@
         <v>44</v>
       </c>
       <c r="C50" t="n">
-        <v>0.0015092503205241</v>
+        <v>0.00153855747675692</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0000455267014720686</v>
+        <v>0.0000464199050722866</v>
       </c>
     </row>
     <row r="51">
@@ -2320,7 +2320,7 @@
         <v>63</v>
       </c>
       <c r="C51" t="n">
-        <v>0.00137694062383486</v>
+        <v>0.00140365878502415</v>
       </c>
       <c r="D51"/>
     </row>
@@ -2332,7 +2332,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00103715174113462</v>
+        <v>0.00105955736318937</v>
       </c>
       <c r="D52"/>
     </row>
@@ -2344,7 +2344,7 @@
         <v>68</v>
       </c>
       <c r="C53" t="n">
-        <v>0.000688449962840732</v>
+        <v>0.000701829392512073</v>
       </c>
       <c r="D53"/>
     </row>
@@ -2356,7 +2356,7 @@
         <v>75</v>
       </c>
       <c r="C54" t="n">
-        <v>0.000518575870567309</v>
+        <v>0.000529778681594684</v>
       </c>
       <c r="D54"/>
     </row>
@@ -2393,10 +2393,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="n">
-        <v>21.7609266136752</v>
+        <v>21.7622773575215</v>
       </c>
       <c r="D2" t="n">
-        <v>0.240627134478429</v>
+        <v>0.24065772968727</v>
       </c>
     </row>
     <row r="3">
@@ -2407,10 +2407,10 @@
         <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>10.0832045034164</v>
+        <v>10.0835695604787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.122239385124135</v>
+        <v>0.122638013213039</v>
       </c>
     </row>
     <row r="4">
@@ -2421,10 +2421,10 @@
         <v>7</v>
       </c>
       <c r="C4" t="n">
-        <v>7.67074898905725</v>
+        <v>7.67035526264039</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0911385631254121</v>
+        <v>0.0911317981196219</v>
       </c>
     </row>
     <row r="5">
@@ -2435,10 +2435,10 @@
         <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6.91857086316109</v>
+        <v>6.91866081336333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.124172617812163</v>
+        <v>0.124170619654835</v>
       </c>
     </row>
     <row r="6">
@@ -2449,10 +2449,10 @@
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>5.78196952153187</v>
+        <v>5.78175384328398</v>
       </c>
       <c r="D6" t="n">
-        <v>0.173895046899155</v>
+        <v>0.173891851031029</v>
       </c>
     </row>
     <row r="7">
@@ -2463,10 +2463,10 @@
         <v>12</v>
       </c>
       <c r="C7" t="n">
-        <v>4.78101842415757</v>
+        <v>4.78105021624774</v>
       </c>
       <c r="D7" t="n">
-        <v>0.260105197121463</v>
+        <v>0.260110951841298</v>
       </c>
     </row>
     <row r="8">
@@ -2477,10 +2477,10 @@
         <v>28</v>
       </c>
       <c r="C8" t="n">
-        <v>4.75112364897646</v>
+        <v>4.75077424714615</v>
       </c>
       <c r="D8" t="n">
-        <v>0.129801582746227</v>
+        <v>0.129793138447533</v>
       </c>
     </row>
     <row r="9">
@@ -2491,10 +2491,10 @@
         <v>9</v>
       </c>
       <c r="C9" t="n">
-        <v>4.31632550610984</v>
+        <v>4.31494152258331</v>
       </c>
       <c r="D9" t="n">
-        <v>0.725800213673338</v>
+        <v>0.725507562537395</v>
       </c>
     </row>
     <row r="10">
@@ -2505,10 +2505,10 @@
         <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>3.28238491504789</v>
+        <v>3.28226886000876</v>
       </c>
       <c r="D10" t="n">
-        <v>0.106971006927844</v>
+        <v>0.106967135986772</v>
       </c>
     </row>
     <row r="11">
@@ -2519,10 +2519,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>3.02506808672434</v>
+        <v>3.02516408871599</v>
       </c>
       <c r="D11" t="n">
-        <v>0.233309854205774</v>
+        <v>0.233320384039409</v>
       </c>
     </row>
     <row r="12">
@@ -2533,10 +2533,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>2.96974705539577</v>
+        <v>2.97005297943848</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0686003398598993</v>
+        <v>0.0686106472512165</v>
       </c>
     </row>
     <row r="13">
@@ -2547,10 +2547,10 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>2.36803476006497</v>
+        <v>2.36796288589534</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0847669645851135</v>
+        <v>0.0847630239866693</v>
       </c>
     </row>
     <row r="14">
@@ -2561,10 +2561,10 @@
         <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>2.26675503353507</v>
+        <v>2.26695125312262</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0418533205527473</v>
+        <v>0.0418574721223817</v>
       </c>
     </row>
     <row r="15">
@@ -2575,10 +2575,10 @@
         <v>41</v>
       </c>
       <c r="C15" t="n">
-        <v>2.16120215614226</v>
+        <v>2.16190915247882</v>
       </c>
       <c r="D15" t="n">
-        <v>0.630839632185262</v>
+        <v>0.631046876611651</v>
       </c>
     </row>
     <row r="16">
@@ -2589,10 +2589,10 @@
         <v>19</v>
       </c>
       <c r="C16" t="n">
-        <v>1.78431039450407</v>
+        <v>1.78449052469228</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0132479013162543</v>
+        <v>0.0132512817326122</v>
       </c>
     </row>
     <row r="17">
@@ -2603,10 +2603,10 @@
         <v>22</v>
       </c>
       <c r="C17" t="n">
-        <v>1.56894865858386</v>
+        <v>1.568986544644</v>
       </c>
       <c r="D17" t="n">
-        <v>0.158045752393243</v>
+        <v>0.158054034060133</v>
       </c>
     </row>
     <row r="18">
@@ -2617,10 +2617,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>1.43192150213586</v>
+        <v>1.43198268437643</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0873671621098392</v>
+        <v>0.087374396443473</v>
       </c>
     </row>
     <row r="19">
@@ -2631,10 +2631,10 @@
         <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>1.30185458681485</v>
+        <v>1.30212288353511</v>
       </c>
       <c r="D19" t="n">
-        <v>0.12398872214353</v>
+        <v>0.124013734188933</v>
       </c>
     </row>
     <row r="20">
@@ -2645,10 +2645,10 @@
         <v>30</v>
       </c>
       <c r="C20" t="n">
-        <v>1.23583942632259</v>
+        <v>1.23597398972075</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0133493632071244</v>
+        <v>0.0133513804935949</v>
       </c>
     </row>
     <row r="21">
@@ -2659,10 +2659,10 @@
         <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>1.15782568183839</v>
+        <v>1.15781211665459</v>
       </c>
       <c r="D21" t="n">
-        <v>0.388147454124298</v>
+        <v>0.388147147303828</v>
       </c>
     </row>
     <row r="22">
@@ -2673,10 +2673,10 @@
         <v>24</v>
       </c>
       <c r="C22" t="n">
-        <v>0.914810625981458</v>
+        <v>0.914748471908951</v>
       </c>
       <c r="D22" t="n">
-        <v>0.112719322261636</v>
+        <v>0.112713526040406</v>
       </c>
     </row>
     <row r="23">
@@ -2687,10 +2687,10 @@
         <v>46</v>
       </c>
       <c r="C23" t="n">
-        <v>0.837110437409499</v>
+        <v>0.837026874985027</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0246533465768839</v>
+        <v>0.0246501059907574</v>
       </c>
     </row>
     <row r="24">
@@ -2701,10 +2701,10 @@
         <v>13</v>
       </c>
       <c r="C24" t="n">
-        <v>0.81902960218412</v>
+        <v>0.817827013939666</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0866843549646087</v>
+        <v>0.0910654503357963</v>
       </c>
     </row>
     <row r="25">
@@ -2715,10 +2715,10 @@
         <v>20</v>
       </c>
       <c r="C25" t="n">
-        <v>0.70854617892614</v>
+        <v>0.708597430077996</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0723915203508276</v>
+        <v>0.0723993903413844</v>
       </c>
     </row>
     <row r="26">
@@ -2729,10 +2729,10 @@
         <v>34</v>
       </c>
       <c r="C26" t="n">
-        <v>0.660269625967694</v>
+        <v>0.660353895473854</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0185273727082479</v>
+        <v>0.0185283817921405</v>
       </c>
     </row>
     <row r="27">
@@ -2743,10 +2743,10 @@
         <v>45</v>
       </c>
       <c r="C27" t="n">
-        <v>0.630804205125401</v>
+        <v>0.630698100890269</v>
       </c>
       <c r="D27" t="n">
-        <v>0.21514285032078</v>
+        <v>0.215099761008479</v>
       </c>
     </row>
     <row r="28">
@@ -2757,10 +2757,10 @@
         <v>51</v>
       </c>
       <c r="C28" t="n">
-        <v>0.406629786645901</v>
+        <v>0.406617206121492</v>
       </c>
       <c r="D28" t="n">
-        <v>0.17598432539977</v>
+        <v>0.175977369525517</v>
       </c>
     </row>
     <row r="29">
@@ -2771,10 +2771,10 @@
         <v>63</v>
       </c>
       <c r="C29" t="n">
-        <v>0.376478799111195</v>
+        <v>0.376460428719311</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0569277071811371</v>
+        <v>0.0569255066041069</v>
       </c>
     </row>
     <row r="30">
@@ -2785,10 +2785,10 @@
         <v>23</v>
       </c>
       <c r="C30" t="n">
-        <v>0.319907100323329</v>
+        <v>0.319966284722752</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0792373807900135</v>
+        <v>0.0792516795713162</v>
       </c>
     </row>
     <row r="31">
@@ -2799,10 +2799,10 @@
         <v>43</v>
       </c>
       <c r="C31" t="n">
-        <v>0.311547220728577</v>
+        <v>0.311533277594606</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0172972008546067</v>
+        <v>0.017295263988654</v>
       </c>
     </row>
     <row r="32">
@@ -2813,10 +2813,10 @@
         <v>18</v>
       </c>
       <c r="C32" t="n">
-        <v>0.303531346920234</v>
+        <v>0.303578981210747</v>
       </c>
       <c r="D32" t="n">
-        <v>0.017466941321902</v>
+        <v>0.0174706884831037</v>
       </c>
     </row>
     <row r="33">
@@ -2827,10 +2827,10 @@
         <v>25</v>
       </c>
       <c r="C33" t="n">
-        <v>0.276621159496425</v>
+        <v>0.276639768738065</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0136147728685635</v>
+        <v>0.0136172519351224</v>
       </c>
     </row>
     <row r="34">
@@ -2841,10 +2841,10 @@
         <v>54</v>
       </c>
       <c r="C34" t="n">
-        <v>0.257536867560212</v>
+        <v>0.257546713674983</v>
       </c>
       <c r="D34" t="n">
-        <v>0.00630636905983868</v>
+        <v>0.00630700331476103</v>
       </c>
     </row>
     <row r="35">
@@ -2855,10 +2855,10 @@
         <v>62</v>
       </c>
       <c r="C35" t="n">
-        <v>0.240955188548261</v>
+        <v>0.240932634902632</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0196478778738606</v>
+        <v>0.019645659674528</v>
       </c>
     </row>
     <row r="36">
@@ -2869,10 +2869,10 @@
         <v>44</v>
       </c>
       <c r="C36" t="n">
-        <v>0.230585283865868</v>
+        <v>0.230564123421666</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0509844526870072</v>
+        <v>0.0509783767753283</v>
       </c>
     </row>
     <row r="37">
@@ -2883,10 +2883,10 @@
         <v>31</v>
       </c>
       <c r="C37" t="n">
-        <v>0.219742906044752</v>
+        <v>0.21975122573986</v>
       </c>
       <c r="D37" t="n">
-        <v>0.00600844586702114</v>
+        <v>0.0060086872243454</v>
       </c>
     </row>
     <row r="38">
@@ -2897,10 +2897,10 @@
         <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>0.199526690045392</v>
+        <v>0.199526182780347</v>
       </c>
       <c r="D38" t="n">
-        <v>0.00331135266480902</v>
+        <v>0.00331114598644298</v>
       </c>
     </row>
     <row r="39">
@@ -2911,10 +2911,10 @@
         <v>36</v>
       </c>
       <c r="C39" t="n">
-        <v>0.180419394007164</v>
+        <v>0.18040569029904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0166865917056073</v>
+        <v>0.0166850776816214</v>
       </c>
     </row>
     <row r="40">
@@ -2925,10 +2925,10 @@
         <v>35</v>
       </c>
       <c r="C40" t="n">
-        <v>0.175302426010932</v>
+        <v>0.175282668877571</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0704758478739547</v>
+        <v>0.0704671562035202</v>
       </c>
     </row>
     <row r="41">
@@ -2939,10 +2939,10 @@
         <v>52</v>
       </c>
       <c r="C41" t="n">
-        <v>0.169975364996057</v>
+        <v>0.169955366435392</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0222827397611038</v>
+        <v>0.0222798777174903</v>
       </c>
     </row>
     <row r="42">
@@ -2953,10 +2953,10 @@
         <v>50</v>
       </c>
       <c r="C42" t="n">
-        <v>0.158651012341907</v>
+        <v>0.158673366659809</v>
       </c>
       <c r="D42" t="n">
-        <v>0.045737570407468</v>
+        <v>0.0457539772131932</v>
       </c>
     </row>
     <row r="43">
@@ -2967,10 +2967,10 @@
         <v>27</v>
       </c>
       <c r="C43" t="n">
-        <v>0.137410891541032</v>
+        <v>0.137395260037261</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0449355261351212</v>
+        <v>0.0449289816918205</v>
       </c>
     </row>
     <row r="44">
@@ -2981,10 +2981,10 @@
         <v>37</v>
       </c>
       <c r="C44" t="n">
-        <v>0.137143232701889</v>
+        <v>0.137167318408933</v>
       </c>
       <c r="D44" t="n">
-        <v>0.00308459967368937</v>
+        <v>0.00308513793538259</v>
       </c>
     </row>
     <row r="45">
@@ -2995,10 +2995,10 @@
         <v>26</v>
       </c>
       <c r="C45" t="n">
-        <v>0.08329335259299</v>
+        <v>0.0832918371541882</v>
       </c>
       <c r="D45" t="n">
-        <v>0.00412519462388737</v>
+        <v>0.00412483158417483</v>
       </c>
     </row>
     <row r="46">
@@ -3009,10 +3009,10 @@
         <v>59</v>
       </c>
       <c r="C46" t="n">
-        <v>0.0692411801897809</v>
+        <v>0.0692410464152097</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0243421446622777</v>
+        <v>0.0243414152156006</v>
       </c>
     </row>
     <row r="47">
@@ -3023,10 +3023,10 @@
         <v>49</v>
       </c>
       <c r="C47" t="n">
-        <v>0.067218041652683</v>
+        <v>0.0672108440905825</v>
       </c>
       <c r="D47" t="n">
-        <v>0.00668684478327204</v>
+        <v>0.00668616124790953</v>
       </c>
     </row>
     <row r="48">
@@ -3037,7 +3037,7 @@
         <v>32</v>
       </c>
       <c r="C48" t="n">
-        <v>0.06156481136528</v>
+        <v>0.0615545147950379</v>
       </c>
       <c r="D48"/>
     </row>
@@ -3049,10 +3049,10 @@
         <v>61</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0558564601377837</v>
+        <v>0.0558554742148481</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0072784081124607</v>
+        <v>0.00727819198305638</v>
       </c>
     </row>
     <row r="50">
@@ -3063,10 +3063,10 @@
         <v>66</v>
       </c>
       <c r="C50" t="n">
-        <v>0.041275304519162</v>
+        <v>0.0412794290949981</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0080909810456354</v>
+        <v>0.00809159300126105</v>
       </c>
     </row>
     <row r="51">
@@ -3077,10 +3077,10 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>0.0357424290263582</v>
+        <v>0.0357480677974404</v>
       </c>
       <c r="D51" t="n">
-        <v>0.00168638120545988</v>
+        <v>0.00168680940639728</v>
       </c>
     </row>
     <row r="52">
@@ -3091,10 +3091,10 @@
         <v>70</v>
       </c>
       <c r="C52" t="n">
-        <v>0.0329751577979992</v>
+        <v>0.0329700569728601</v>
       </c>
       <c r="D52" t="n">
-        <v>0.00303624128538705</v>
+        <v>0.00303563958218496</v>
       </c>
     </row>
     <row r="53">
@@ -3105,10 +3105,10 @@
         <v>48</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0326582679579259</v>
+        <v>0.0326619136604909</v>
       </c>
       <c r="D53" t="n">
-        <v>0.00209412826448036</v>
+        <v>0.00209457650402667</v>
       </c>
     </row>
     <row r="54">
@@ -3119,7 +3119,7 @@
         <v>60</v>
       </c>
       <c r="C54" t="n">
-        <v>0.0316309736631204</v>
+        <v>0.0316297890797849</v>
       </c>
       <c r="D54"/>
     </row>
@@ -3131,10 +3131,10 @@
         <v>73</v>
       </c>
       <c r="C55" t="n">
-        <v>0.0313758170533332</v>
+        <v>0.0313841297664091</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00523947935992204</v>
+        <v>0.00524152469478577</v>
       </c>
     </row>
     <row r="56">
@@ -3145,10 +3145,10 @@
         <v>55</v>
       </c>
       <c r="C56" t="n">
-        <v>0.0298202618941446</v>
+        <v>0.0298250290235258</v>
       </c>
       <c r="D56" t="n">
-        <v>0.00668946759658577</v>
+        <v>0.00669114910307872</v>
       </c>
     </row>
     <row r="57">
@@ -3159,10 +3159,10 @@
         <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>0.0295457685029536</v>
+        <v>0.0295461004520193</v>
       </c>
       <c r="D57" t="n">
-        <v>0.00598291523636964</v>
+        <v>0.00598137732196592</v>
       </c>
     </row>
     <row r="58">
@@ -3173,10 +3173,10 @@
         <v>58</v>
       </c>
       <c r="C58" t="n">
-        <v>0.0256615203212098</v>
+        <v>0.0256641501038899</v>
       </c>
       <c r="D58" t="n">
-        <v>0.00664478539283624</v>
+        <v>0.00664577834495545</v>
       </c>
     </row>
     <row r="59">
@@ -3187,10 +3187,10 @@
         <v>47</v>
       </c>
       <c r="C59" t="n">
-        <v>0.0178994139860595</v>
+        <v>0.0179009714449529</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00235547475936501</v>
+        <v>0.00235512932184248</v>
       </c>
     </row>
     <row r="60">
@@ -3201,10 +3201,10 @@
         <v>53</v>
       </c>
       <c r="C60" t="n">
-        <v>0.0140552285037183</v>
+        <v>0.0140572890748737</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00201327935472589</v>
+        <v>0.0020135781075336</v>
       </c>
     </row>
     <row r="61">
@@ -3215,10 +3215,10 @@
         <v>65</v>
       </c>
       <c r="C61" t="n">
-        <v>0.0114864371120666</v>
+        <v>0.0114842257669918</v>
       </c>
       <c r="D61" t="n">
-        <v>0.00438291868901427</v>
+        <v>0.00438250764268453</v>
       </c>
     </row>
     <row r="62">
@@ -3229,10 +3229,10 @@
         <v>39</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00764347406992903</v>
+        <v>0.00764209855422093</v>
       </c>
       <c r="D62" t="n">
-        <v>0.00492737014416636</v>
+        <v>0.00492660482862357</v>
       </c>
     </row>
     <row r="63">
@@ -3243,7 +3243,7 @@
         <v>82</v>
       </c>
       <c r="C63" t="n">
-        <v>0.00654644511804976</v>
+        <v>0.00654815647051074</v>
       </c>
       <c r="D63"/>
     </row>
@@ -3255,7 +3255,7 @@
         <v>40</v>
       </c>
       <c r="C64" t="n">
-        <v>0.00591344335439638</v>
+        <v>0.00591442986738659</v>
       </c>
       <c r="D64"/>
     </row>
@@ -3267,10 +3267,10 @@
         <v>68</v>
       </c>
       <c r="C65" t="n">
-        <v>0.00558355119579296</v>
+        <v>0.00558395893937707</v>
       </c>
       <c r="D65" t="n">
-        <v>0.00115410349329897</v>
+        <v>0.00115438021349579</v>
       </c>
     </row>
     <row r="66">
@@ -3281,7 +3281,7 @@
         <v>57</v>
       </c>
       <c r="C66" t="n">
-        <v>0.00543441349094345</v>
+        <v>0.00543327530447121</v>
       </c>
       <c r="D66"/>
     </row>
@@ -3293,7 +3293,7 @@
         <v>74</v>
       </c>
       <c r="C67" t="n">
-        <v>0.00227296086236</v>
+        <v>0.00227236253405944</v>
       </c>
       <c r="D67"/>
     </row>
@@ -3305,7 +3305,7 @@
         <v>75</v>
       </c>
       <c r="C68" t="n">
-        <v>0.00131995759266029</v>
+        <v>0.00131999530673519</v>
       </c>
       <c r="D68"/>
     </row>
@@ -3317,10 +3317,10 @@
         <v>77</v>
       </c>
       <c r="C69" t="n">
-        <v>0.00128045054789576</v>
+        <v>0.00128144962202281</v>
       </c>
       <c r="D69" t="n">
-        <v>0.000133274109538564</v>
+        <v>0.00013329477761492</v>
       </c>
     </row>
     <row r="70">
@@ -3331,7 +3331,7 @@
         <v>80</v>
       </c>
       <c r="C70" t="n">
-        <v>0.00123255311809684</v>
+        <v>0.00123373961745808</v>
       </c>
       <c r="D70"/>
     </row>
@@ -3343,7 +3343,7 @@
         <v>69</v>
       </c>
       <c r="C71" t="n">
-        <v>0.000820479638527545</v>
+        <v>0.000820123314788007</v>
       </c>
       <c r="D71"/>
     </row>
@@ -3355,7 +3355,7 @@
         <v>71</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00033617105601325</v>
+        <v>0.000336469391912891</v>
       </c>
       <c r="D72"/>
     </row>
